--- a/finish.xlsx
+++ b/finish.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>batchsize</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,7 @@
           <t>DNANet</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +457,7 @@
           <t>res_UNet</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +470,7 @@
           <t>ISTDU-Net</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +483,7 @@
           <t>L2SKNet</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +496,7 @@
           <t>MSHNet</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +509,7 @@
           <t>DNANet</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +522,7 @@
           <t>res_UNet</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +535,7 @@
           <t>ISTDU-Net</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +548,7 @@
           <t>L2SKNet</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +561,7 @@
           <t>MSHNet</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +574,7 @@
           <t>DTUM+DNANet</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +587,7 @@
           <t>DTUM+res_UNet</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +600,7 @@
           <t>DTUM+ISTDU-Net</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +613,7 @@
           <t>DTUM+L2SKNet</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +626,7 @@
           <t>DTUM+MSHNet</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +639,7 @@
           <t>DTUM+res_UNet</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +652,7 @@
           <t>DTUM+res_UNet</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,6 +665,7 @@
           <t>DTUM+L2SKNet</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -655,6 +678,7 @@
           <t>DTUM+MSHNet</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -667,6 +691,7 @@
           <t>RFR+DNANet</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -679,6 +704,7 @@
           <t>RFR+res_UNet</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -691,6 +717,7 @@
           <t>RFR+ISTDU-Net</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -703,6 +730,7 @@
           <t>RFR+L2SKNet</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -715,6 +743,7 @@
           <t>RFR+MSHNet</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -727,6 +756,7 @@
           <t>RFR+res_UNet</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -739,6 +769,7 @@
           <t>RFR+res_UNet</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -750,6 +781,121 @@
         <is>
           <t>RFR+L2SKNet</t>
         </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DQAligner</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DQAligner</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/finish.xlsx
+++ b/finish.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,51 @@
         <v>4</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finish.xlsx
+++ b/finish.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,141 @@
         <v>4</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SDecNet</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUDT-MIRSDT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IRDST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>STDecNet</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
